--- a/SUKSES_Data.xlsx
+++ b/SUKSES_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1F5D641-C553-434B-A15C-17E81E117DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83C661E-D849-4643-AF27-39054A19A6FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="113">
   <si>
     <t>Kumpulan</t>
   </si>
@@ -358,6 +358,9 @@
   </si>
   <si>
     <t>Kehadiran</t>
+  </si>
+  <si>
+    <t>Kelestarian TH</t>
   </si>
 </sst>
 </file>
@@ -434,7 +437,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -442,7 +445,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -745,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1497,10 +1499,10 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" s="7" t="s">
+      <c r="A38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>110</v>
       </c>
       <c r="C38" t="s">
@@ -1509,18 +1511,18 @@
       <c r="D38" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B39" s="7" t="s">
+      <c r="A39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>110</v>
       </c>
       <c r="C39" t="s">
@@ -1529,18 +1531,18 @@
       <c r="D39" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="3" t="s">
         <v>110</v>
       </c>
       <c r="C40" t="s">
@@ -1549,18 +1551,18 @@
       <c r="D40" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41" s="7" t="s">
+      <c r="A41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>110</v>
       </c>
       <c r="C41" t="s">
@@ -1569,18 +1571,18 @@
       <c r="D41" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="3" t="s">
         <v>110</v>
       </c>
       <c r="C42" t="s">
@@ -1589,11 +1591,171 @@
       <c r="D42" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43" t="s">
+        <v>33</v>
+      </c>
+      <c r="E43" t="s">
+        <v>111</v>
+      </c>
+      <c r="F43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" t="s">
+        <v>112</v>
+      </c>
+      <c r="C44" t="s">
+        <v>60</v>
+      </c>
+      <c r="D44" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" t="s">
+        <v>111</v>
+      </c>
+      <c r="F44">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45" t="s">
+        <v>36</v>
+      </c>
+      <c r="D45" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" t="s">
+        <v>111</v>
+      </c>
+      <c r="F45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" t="s">
+        <v>111</v>
+      </c>
+      <c r="F46">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" t="s">
+        <v>63</v>
+      </c>
+      <c r="D47" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" t="s">
+        <v>111</v>
+      </c>
+      <c r="F47">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" t="s">
+        <v>33</v>
+      </c>
+      <c r="E48" t="s">
+        <v>111</v>
+      </c>
+      <c r="F48">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" t="s">
+        <v>112</v>
+      </c>
+      <c r="C49" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" t="s">
+        <v>33</v>
+      </c>
+      <c r="E49" t="s">
+        <v>111</v>
+      </c>
+      <c r="F49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" t="s">
+        <v>43</v>
+      </c>
+      <c r="D50" t="s">
+        <v>33</v>
+      </c>
+      <c r="E50" t="s">
+        <v>111</v>
+      </c>
+      <c r="F50">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
